--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5644"/>
+  <dimension ref="A1:B5651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56870,6 +56870,76 @@
         <v>-179705113.13</v>
       </c>
     </row>
+    <row r="5645">
+      <c r="A5645" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B5645" t="n">
+        <v>737472887.33</v>
+      </c>
+    </row>
+    <row r="5646">
+      <c r="A5646" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B5646" t="n">
+        <v>307934938.8</v>
+      </c>
+    </row>
+    <row r="5647">
+      <c r="A5647" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B5647" t="n">
+        <v>364152585.86</v>
+      </c>
+    </row>
+    <row r="5648">
+      <c r="A5648" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B5648" t="n">
+        <v>1202371778.3</v>
+      </c>
+    </row>
+    <row r="5649">
+      <c r="A5649" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B5649" t="n">
+        <v>885088717.5599999</v>
+      </c>
+    </row>
+    <row r="5650">
+      <c r="A5650" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B5650" t="n">
+        <v>1854052709.94</v>
+      </c>
+    </row>
+    <row r="5651">
+      <c r="A5651" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B5651" t="n">
+        <v>783272441.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5651"/>
+  <dimension ref="A1:B5653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56940,6 +56940,26 @@
         <v>783272441.48</v>
       </c>
     </row>
+    <row r="5652">
+      <c r="A5652" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B5652" t="n">
+        <v>1023460774.36</v>
+      </c>
+    </row>
+    <row r="5653">
+      <c r="A5653" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B5653" t="n">
+        <v>607042422.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5653"/>
+  <dimension ref="A1:B5660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56960,6 +56960,76 @@
         <v>607042422.85</v>
       </c>
     </row>
+    <row r="5654">
+      <c r="A5654" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B5654" t="n">
+        <v>417127029.87</v>
+      </c>
+    </row>
+    <row r="5655">
+      <c r="A5655" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B5655" t="n">
+        <v>1103421745.54</v>
+      </c>
+    </row>
+    <row r="5656">
+      <c r="A5656" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5656" t="n">
+        <v>1387399723.49</v>
+      </c>
+    </row>
+    <row r="5657">
+      <c r="A5657" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B5657" t="n">
+        <v>1224509619.5</v>
+      </c>
+    </row>
+    <row r="5658">
+      <c r="A5658" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B5658" t="n">
+        <v>1185716720.05</v>
+      </c>
+    </row>
+    <row r="5659">
+      <c r="A5659" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B5659" t="n">
+        <v>721006646.66</v>
+      </c>
+    </row>
+    <row r="5660">
+      <c r="A5660" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B5660" t="n">
+        <v>534126008.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5660"/>
+  <dimension ref="A1:B5664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57030,6 +57030,46 @@
         <v>534126008.17</v>
       </c>
     </row>
+    <row r="5661">
+      <c r="A5661" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B5661" t="n">
+        <v>66837350.35</v>
+      </c>
+    </row>
+    <row r="5662">
+      <c r="A5662" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B5662" t="n">
+        <v>622410096.23</v>
+      </c>
+    </row>
+    <row r="5663">
+      <c r="A5663" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B5663" t="n">
+        <v>1116325585.27</v>
+      </c>
+    </row>
+    <row r="5664">
+      <c r="A5664" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B5664" t="n">
+        <v>1073076213.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5664"/>
+  <dimension ref="A1:B5670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57070,6 +57070,66 @@
         <v>1073076213.84</v>
       </c>
     </row>
+    <row r="5665">
+      <c r="A5665" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B5665" t="n">
+        <v>1199201032.46</v>
+      </c>
+    </row>
+    <row r="5666">
+      <c r="A5666" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B5666" t="n">
+        <v>5153237375.71</v>
+      </c>
+    </row>
+    <row r="5667">
+      <c r="A5667" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B5667" t="n">
+        <v>265810883.57</v>
+      </c>
+    </row>
+    <row r="5668">
+      <c r="A5668" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B5668" t="n">
+        <v>455486112.12</v>
+      </c>
+    </row>
+    <row r="5669">
+      <c r="A5669" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B5669" t="n">
+        <v>689462537.54</v>
+      </c>
+    </row>
+    <row r="5670">
+      <c r="A5670" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B5670" t="n">
+        <v>500885095.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5670"/>
+  <dimension ref="A1:B5671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57130,6 +57130,16 @@
         <v>500885095.57</v>
       </c>
     </row>
+    <row r="5671">
+      <c r="A5671" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B5671" t="n">
+        <v>710738564.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5671"/>
+  <dimension ref="A1:B5672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57140,6 +57140,16 @@
         <v>710738564.72</v>
       </c>
     </row>
+    <row r="5672">
+      <c r="A5672" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B5672" t="n">
+        <v>999024231.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5672"/>
+  <dimension ref="A1:B5675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57150,6 +57150,36 @@
         <v>999024231.77</v>
       </c>
     </row>
+    <row r="5673">
+      <c r="A5673" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B5673" t="n">
+        <v>1728596936.5</v>
+      </c>
+    </row>
+    <row r="5674">
+      <c r="A5674" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B5674" t="n">
+        <v>1552771435.19</v>
+      </c>
+    </row>
+    <row r="5675">
+      <c r="A5675" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B5675" t="n">
+        <v>1156439840.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5675"/>
+  <dimension ref="A1:B5677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57180,6 +57180,26 @@
         <v>1156439840.34</v>
       </c>
     </row>
+    <row r="5676">
+      <c r="A5676" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B5676" t="n">
+        <v>2349326700.17</v>
+      </c>
+    </row>
+    <row r="5677">
+      <c r="A5677" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B5677" t="n">
+        <v>2645308623.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5677"/>
+  <dimension ref="A1:B5678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57200,6 +57200,16 @@
         <v>2645308623.74</v>
       </c>
     </row>
+    <row r="5678">
+      <c r="A5678" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B5678" t="n">
+        <v>2679397661.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5678"/>
+  <dimension ref="A1:B5679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57210,6 +57210,16 @@
         <v>2679397661.62</v>
       </c>
     </row>
+    <row r="5679">
+      <c r="A5679" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B5679" t="n">
+        <v>6581111571.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5679"/>
+  <dimension ref="A1:B5683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57220,6 +57220,46 @@
         <v>6581111571.44</v>
       </c>
     </row>
+    <row r="5680">
+      <c r="A5680" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B5680" t="n">
+        <v>4112688255.37</v>
+      </c>
+    </row>
+    <row r="5681">
+      <c r="A5681" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B5681" t="n">
+        <v>1204057155.57</v>
+      </c>
+    </row>
+    <row r="5682">
+      <c r="A5682" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B5682" t="n">
+        <v>706010036.28</v>
+      </c>
+    </row>
+    <row r="5683">
+      <c r="A5683" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B5683" t="n">
+        <v>1771761332.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5683"/>
+  <dimension ref="A1:B5684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57260,6 +57260,16 @@
         <v>1771761332.69</v>
       </c>
     </row>
+    <row r="5684">
+      <c r="A5684" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B5684" t="n">
+        <v>1708453644.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5684"/>
+  <dimension ref="A1:B5688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57270,6 +57270,46 @@
         <v>1708453644.4</v>
       </c>
     </row>
+    <row r="5685">
+      <c r="A5685" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B5685" t="n">
+        <v>1475550631.56</v>
+      </c>
+    </row>
+    <row r="5686">
+      <c r="A5686" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B5686" t="n">
+        <v>1778770199.58</v>
+      </c>
+    </row>
+    <row r="5687">
+      <c r="A5687" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B5687" t="n">
+        <v>1841723136.72</v>
+      </c>
+    </row>
+    <row r="5688">
+      <c r="A5688" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B5688" t="n">
+        <v>446756501.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5688"/>
+  <dimension ref="A1:B5692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57310,6 +57310,46 @@
         <v>446756501.52</v>
       </c>
     </row>
+    <row r="5689">
+      <c r="A5689" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B5689" t="n">
+        <v>393570710.34</v>
+      </c>
+    </row>
+    <row r="5690">
+      <c r="A5690" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B5690" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5691">
+      <c r="A5691" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B5691" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5692">
+      <c r="A5692" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B5692" t="n">
+        <v>729860086.3200001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5692"/>
+  <dimension ref="A1:B5693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57350,6 +57350,16 @@
         <v>729860086.3200001</v>
       </c>
     </row>
+    <row r="5693">
+      <c r="A5693" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B5693" t="n">
+        <v>892916267.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5693"/>
+  <dimension ref="A1:B5696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57360,6 +57360,36 @@
         <v>892916267.91</v>
       </c>
     </row>
+    <row r="5694">
+      <c r="A5694" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B5694" t="n">
+        <v>1519005137.81</v>
+      </c>
+    </row>
+    <row r="5695">
+      <c r="A5695" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B5695" t="n">
+        <v>293827401.02</v>
+      </c>
+    </row>
+    <row r="5696">
+      <c r="A5696" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B5696" t="n">
+        <v>206615652.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5696"/>
+  <dimension ref="A1:B5698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57390,6 +57390,26 @@
         <v>206615652.93</v>
       </c>
     </row>
+    <row r="5697">
+      <c r="A5697" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B5697" t="n">
+        <v>1453886053.67</v>
+      </c>
+    </row>
+    <row r="5698">
+      <c r="A5698" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B5698" t="n">
+        <v>1904490885.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5698"/>
+  <dimension ref="A1:B5699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57410,6 +57410,16 @@
         <v>1904490885.44</v>
       </c>
     </row>
+    <row r="5699">
+      <c r="A5699" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B5699" t="n">
+        <v>1402051148.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5699"/>
+  <dimension ref="A1:B5700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57420,6 +57420,16 @@
         <v>1402051148.44</v>
       </c>
     </row>
+    <row r="5700">
+      <c r="A5700" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B5700" t="n">
+        <v>933968859.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5700"/>
+  <dimension ref="A1:B5702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57430,6 +57430,26 @@
         <v>933968859.38</v>
       </c>
     </row>
+    <row r="5701">
+      <c r="A5701" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B5701" t="n">
+        <v>1008260482.41</v>
+      </c>
+    </row>
+    <row r="5702">
+      <c r="A5702" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B5702" t="n">
+        <v>515793680.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5702"/>
+  <dimension ref="A1:B5707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57450,6 +57450,56 @@
         <v>515793680.33</v>
       </c>
     </row>
+    <row r="5703">
+      <c r="A5703" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B5703" t="n">
+        <v>501855441.15</v>
+      </c>
+    </row>
+    <row r="5704">
+      <c r="A5704" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B5704" t="n">
+        <v>1002445880.26</v>
+      </c>
+    </row>
+    <row r="5705">
+      <c r="A5705" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B5705" t="n">
+        <v>815400153.87</v>
+      </c>
+    </row>
+    <row r="5706">
+      <c r="A5706" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B5706" t="n">
+        <v>1661216641.88</v>
+      </c>
+    </row>
+    <row r="5707">
+      <c r="A5707" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B5707" t="n">
+        <v>924012238.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5707"/>
+  <dimension ref="A1:B5709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57500,6 +57500,26 @@
         <v>924012238.65</v>
       </c>
     </row>
+    <row r="5708">
+      <c r="A5708" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B5708" t="n">
+        <v>1456702722.32</v>
+      </c>
+    </row>
+    <row r="5709">
+      <c r="A5709" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B5709" t="n">
+        <v>346951345.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5709"/>
+  <dimension ref="A1:B5716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57520,6 +57520,76 @@
         <v>346951345.82</v>
       </c>
     </row>
+    <row r="5710">
+      <c r="A5710" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B5710" t="n">
+        <v>314352995.76</v>
+      </c>
+    </row>
+    <row r="5711">
+      <c r="A5711" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B5711" t="n">
+        <v>917057881.5700001</v>
+      </c>
+    </row>
+    <row r="5712">
+      <c r="A5712" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B5712" t="n">
+        <v>893693098.05</v>
+      </c>
+    </row>
+    <row r="5713">
+      <c r="A5713" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B5713" t="n">
+        <v>1346624187.81</v>
+      </c>
+    </row>
+    <row r="5714">
+      <c r="A5714" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B5714" t="n">
+        <v>1130999999.71</v>
+      </c>
+    </row>
+    <row r="5715">
+      <c r="A5715" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B5715" t="n">
+        <v>1002076476.35</v>
+      </c>
+    </row>
+    <row r="5716">
+      <c r="A5716" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B5716" t="n">
+        <v>509424058.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_nrpl_usd.xlsx
+++ b/data_cripto/btc_nrpl_usd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5716"/>
+  <dimension ref="A1:B5720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57590,6 +57590,46 @@
         <v>509424058.29</v>
       </c>
     </row>
+    <row r="5717">
+      <c r="A5717" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B5717" t="n">
+        <v>287509612.22</v>
+      </c>
+    </row>
+    <row r="5718">
+      <c r="A5718" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B5718" t="n">
+        <v>1151210887.85</v>
+      </c>
+    </row>
+    <row r="5719">
+      <c r="A5719" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B5719" t="n">
+        <v>969624843.33</v>
+      </c>
+    </row>
+    <row r="5720">
+      <c r="A5720" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B5720" t="n">
+        <v>945363710.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
